--- a/product-definitions/spreadsheet/co-h2-concentration.xlsx
+++ b/product-definitions/spreadsheet/co-h2-concentration.xlsx
@@ -207,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -241,11 +241,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -333,7 +328,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8" t="s">
         <v>19</v>
@@ -1965,7 +1960,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>20</v>
@@ -1978,7 +1973,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
@@ -1991,7 +1986,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
@@ -2004,7 +1999,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
@@ -2017,7 +2012,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>26</v>
@@ -2030,7 +2025,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>28</v>
@@ -2043,7 +2038,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="16" t="s">
         <v>30</v>
@@ -2056,7 +2051,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2065,7 +2060,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
@@ -2076,7 +2071,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
         <v>10</v>
@@ -2089,7 +2084,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
         <v>12</v>
@@ -2102,7 +2097,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>2</v>
@@ -2115,7 +2110,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>19</v>
@@ -2128,7 +2123,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>20</v>
@@ -2141,7 +2136,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>22</v>
@@ -2154,7 +2149,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>23</v>
@@ -2167,7 +2162,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>25</v>
@@ -2180,7 +2175,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>26</v>
@@ -2193,7 +2188,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="s">
         <v>28</v>
@@ -2206,7 +2201,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="16" t="s">
         <v>30</v>
@@ -2219,7 +2214,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2228,7 +2223,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
@@ -2239,7 +2234,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
         <v>10</v>
@@ -2252,7 +2247,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
         <v>12</v>
@@ -2265,7 +2260,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>2</v>
@@ -2278,7 +2273,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
         <v>19</v>
@@ -2291,7 +2286,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8" t="s">
         <v>20</v>
@@ -2304,7 +2299,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8" t="s">
         <v>22</v>
@@ -2317,7 +2312,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>23</v>
@@ -2330,7 +2325,7 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
         <v>25</v>
@@ -2343,7 +2338,7 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>26</v>
@@ -2356,7 +2351,7 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8" t="s">
         <v>28</v>
@@ -2369,7 +2364,7 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="16" t="s">
         <v>30</v>
@@ -2382,10 +2377,10 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="21"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="7" t="s">
         <v>41</v>
       </c>
@@ -2396,7 +2391,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8"/>
       <c r="B57" s="8" t="s">
         <v>10</v>
@@ -2409,7 +2404,7 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="8" t="s">
         <v>12</v>
@@ -2422,7 +2417,7 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="9" t="s">
         <v>2</v>
@@ -2437,7 +2432,7 @@
       </c>
       <c r="G59" s="8"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="8"/>
       <c r="B60" s="9" t="s">
         <v>16</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="G60" s="8"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="8" t="s">
         <v>19</v>
@@ -2465,7 +2460,7 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8" t="s">
         <v>20</v>
@@ -2478,7 +2473,7 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8" t="s">
         <v>22</v>
@@ -2491,7 +2486,7 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8" t="s">
         <v>23</v>
@@ -2504,7 +2499,7 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8" t="s">
         <v>25</v>
@@ -2517,7 +2512,7 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="9" t="s">
         <v>26</v>
@@ -2530,7 +2525,7 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="8" t="s">
         <v>28</v>
@@ -2543,7 +2538,7 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="16" t="s">
         <v>30</v>
@@ -2556,7 +2551,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2565,7 +2560,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="7" t="s">
         <v>44</v>
       </c>
@@ -2576,7 +2571,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="8"/>
       <c r="B71" s="8" t="s">
         <v>10</v>
@@ -2589,7 +2584,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8" t="s">
         <v>12</v>
@@ -2602,7 +2597,7 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="9" t="s">
         <v>2</v>
@@ -2617,7 +2612,7 @@
       </c>
       <c r="G73" s="8"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8"/>
       <c r="B74" s="9" t="s">
         <v>16</v>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="G74" s="8"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="8" t="s">
         <v>19</v>
@@ -2645,7 +2640,7 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="8" t="s">
         <v>20</v>
@@ -2658,7 +2653,7 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="8" t="s">
         <v>22</v>
@@ -2671,7 +2666,7 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="8" t="s">
         <v>23</v>
@@ -2684,7 +2679,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="8" t="s">
         <v>25</v>
@@ -2697,7 +2692,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="9" t="s">
         <v>26</v>
@@ -2710,7 +2705,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="8" t="s">
         <v>28</v>
@@ -2723,7 +2718,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="16" t="s">
         <v>30</v>
@@ -2736,7 +2731,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -2745,7 +2740,7 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="7" t="s">
         <v>46</v>
       </c>
@@ -2756,7 +2751,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="8"/>
       <c r="B85" s="8" t="s">
         <v>10</v>
@@ -2769,7 +2764,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="8" t="s">
         <v>12</v>
@@ -2782,7 +2777,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="9"/>
       <c r="B87" s="9" t="s">
         <v>2</v>
@@ -2795,7 +2790,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="8"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8"/>
       <c r="B88" s="8" t="s">
         <v>19</v>
@@ -2808,7 +2803,7 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="8" t="s">
         <v>20</v>
@@ -2821,7 +2816,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="8" t="s">
         <v>22</v>
@@ -2834,7 +2829,7 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="8" t="s">
         <v>23</v>
@@ -2847,7 +2842,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="8" t="s">
         <v>25</v>
@@ -2860,7 +2855,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
       <c r="B93" s="9" t="s">
         <v>26</v>
@@ -2873,7 +2868,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="8" t="s">
         <v>28</v>
@@ -2886,7 +2881,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="16" t="s">
         <v>30</v>
@@ -2899,7 +2894,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -2908,7 +2903,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="7" t="s">
         <v>48</v>
       </c>
@@ -2919,7 +2914,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8"/>
       <c r="B98" s="8" t="s">
         <v>10</v>
@@ -2932,7 +2927,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
       <c r="B99" s="8" t="s">
         <v>12</v>
@@ -2945,7 +2940,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="9"/>
       <c r="B100" s="9" t="s">
         <v>2</v>
@@ -2958,7 +2953,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8"/>
       <c r="B101" s="8" t="s">
         <v>19</v>
@@ -2971,7 +2966,7 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8" t="s">
         <v>20</v>
@@ -2984,7 +2979,7 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
       <c r="B103" s="8" t="s">
         <v>22</v>
@@ -2997,7 +2992,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
       <c r="B104" s="8" t="s">
         <v>23</v>
@@ -3010,7 +3005,7 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
       <c r="B105" s="8" t="s">
         <v>25</v>
@@ -3023,7 +3018,7 @@
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
       <c r="B106" s="9" t="s">
         <v>26</v>
@@ -3036,7 +3031,7 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
       <c r="B107" s="8" t="s">
         <v>28</v>
@@ -3049,7 +3044,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
       <c r="B108" s="16" t="s">
         <v>30</v>
@@ -3062,17 +3057,17 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="C109" s="21"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="22" t="s">
         <v>50</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="23"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2" t="s">
         <v>10</v>
@@ -3081,7 +3076,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2" t="s">
         <v>12</v>
@@ -3090,7 +3085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
         <v>2</v>
@@ -3099,14 +3094,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C114" s="24"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
         <v>20</v>
@@ -3115,7 +3110,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="8" t="s">
         <v>53</v>
@@ -3124,7 +3119,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="6" t="s">
         <v>55</v>
@@ -3133,19 +3128,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="23"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="22" t="s">
         <v>57</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="23"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
         <v>10</v>
@@ -3154,7 +3149,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
         <v>12</v>
@@ -3163,7 +3158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>2</v>
@@ -3172,14 +3167,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C123" s="24"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>20</v>
@@ -3188,7 +3183,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="8" t="s">
         <v>53</v>
@@ -3197,7 +3192,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="6" t="s">
         <v>55</v>
